--- a/premise/data/additional_inventories/lci-ammonia.xlsx
+++ b/premise/data/additional_inventories/lci-ammonia.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDE9D5F-B959-D743-A071-E0F3A0D9069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00F3530-6ABE-744A-BD56-EF4C6094345F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="760" windowWidth="24940" windowHeight="18880" xr2:uid="{65ACB5C6-9A71-F043-B1B5-919D021F4A57}"/>
+    <workbookView xWindow="4680" yWindow="760" windowWidth="24940" windowHeight="18880" xr2:uid="{65ACB5C6-9A71-F043-B1B5-919D021F4A57}"/>
   </bookViews>
   <sheets>
     <sheet name="lci-ammonia_39" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'lci-ammonia_39'!$A$1:$M$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'lci-ammonia_39'!$A$1:$M$403</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="192">
   <si>
     <t>Database</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>Based on Carlo d'Angelo et al., 2021 Supporting Information. Business-as-usual (H2 from steam methane reforming), assuming that the carbon dioxide from syngas and flue gas is compressed and stored underground. Using global markets where available. Water volumes are calculated when needed based on density @ 20C (998.19 kg/m3). Methane, CO and carbon dioxide emissions to water are shown in the source documentation but not available in the biosphere3 database. Includes transport to consumer.</t>
+  </si>
+  <si>
+    <t>ammonia production, with market-average hydrogen</t>
+  </si>
+  <si>
+    <t>market for hydrogen, gaseous, low pressure</t>
   </si>
 </sst>
 </file>
@@ -1097,11 +1103,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1477,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7263A38E-0BDC-2843-B92F-206445D00D40}">
-  <dimension ref="A1:M376"/>
+  <dimension ref="A1:M402"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="53.1640625" customWidth="1"/>
@@ -3761,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
@@ -3769,7 +3774,7 @@
         <v>3</v>
       </c>
       <c r="B138" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.2">
@@ -3962,7 +3967,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -4008,48 +4013,48 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>180</v>
-      </c>
-      <c r="B153">
-        <v>0.17799999999999999</v>
+        <v>51</v>
+      </c>
+      <c r="B153" s="1">
+        <v>3.29E-10</v>
       </c>
       <c r="C153" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G153" t="s">
         <v>26</v>
       </c>
       <c r="H153" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>51</v>
-      </c>
-      <c r="B154" s="1">
-        <v>3.29E-10</v>
+        <v>191</v>
+      </c>
+      <c r="B154">
+        <v>0.17599999999999999</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D154" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G154" t="s">
         <v>26</v>
       </c>
       <c r="H154" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4218,7 +4223,7 @@
         <v>2</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.2">
@@ -4226,7 +4231,7 @@
         <v>3</v>
       </c>
       <c r="B164" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.2">
@@ -4239,78 +4244,90 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>39</v>
-      </c>
-      <c r="B166">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B166" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A170" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B169" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>12</v>
-      </c>
+      <c r="F170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A171" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H171" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I171" s="2"/>
-      <c r="J171" s="2"/>
-      <c r="K171" s="2"/>
-      <c r="L171" s="2"/>
-      <c r="M171" s="2"/>
+      <c r="A171" t="s">
+        <v>17</v>
+      </c>
+      <c r="B171">
+        <v>1.6299999999999999E-3</v>
+      </c>
+      <c r="C171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B172">
-        <v>2.6</v>
+        <v>7.67E-4</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
@@ -4319,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="F172" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="G172" t="s">
         <v>20</v>
@@ -4327,10 +4344,10 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B173">
-        <v>1.2E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="C173" t="s">
         <v>18</v>
@@ -4347,16 +4364,16 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="B174">
-        <v>1.46E-6</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="C174" t="s">
         <v>18</v>
       </c>
       <c r="E174" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F174" t="s">
         <v>19</v>
@@ -4367,19 +4384,19 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="B175">
-        <v>4.5800000000000002E-4</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="C175" t="s">
         <v>18</v>
       </c>
       <c r="E175" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F175" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -4387,19 +4404,19 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B176">
-        <v>2.2399999999999998E-3</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="C176" t="s">
         <v>18</v>
       </c>
       <c r="E176" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F176" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="G176" t="s">
         <v>20</v>
@@ -4407,119 +4424,128 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B177">
-        <v>0.10100000000000001</v>
+        <v>1</v>
       </c>
       <c r="C177" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D177" t="s">
+        <v>6</v>
       </c>
       <c r="E177" t="s">
-        <v>41</v>
-      </c>
-      <c r="F177" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="G177" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="H177" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="B178">
-        <v>4.7699999999999999E-2</v>
+        <v>5.5099999999999998E-5</v>
       </c>
       <c r="C178" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
       </c>
       <c r="E178" t="s">
-        <v>41</v>
-      </c>
-      <c r="F178" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G178" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H178" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="B179">
-        <v>0.14899999999999999</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D179" t="s">
+        <v>38</v>
       </c>
       <c r="E179" t="s">
-        <v>41</v>
-      </c>
-      <c r="F179" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G179" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H179" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>110</v>
-      </c>
-      <c r="B180">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B180" s="1">
+        <v>3.29E-10</v>
       </c>
       <c r="C180" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D180" t="s">
         <v>6</v>
       </c>
       <c r="E180" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G180" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H180" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="B181">
-        <v>5.5099999999999998E-5</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="C181" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D181" t="s">
         <v>6</v>
       </c>
       <c r="E181" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="G181" t="s">
         <v>26</v>
       </c>
       <c r="H181" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B182">
-        <v>0.92</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D182" t="s">
         <v>33</v>
@@ -4531,38 +4557,38 @@
         <v>26</v>
       </c>
       <c r="H182" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>51</v>
-      </c>
-      <c r="B183" s="1">
-        <v>3.29E-10</v>
+        <v>62</v>
+      </c>
+      <c r="B183">
+        <v>-5.5099999999999998E-5</v>
       </c>
       <c r="C183" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E183" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G183" t="s">
         <v>26</v>
       </c>
       <c r="H183" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B184">
-        <v>0.82599999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="C184" t="s">
         <v>25</v>
@@ -4571,266 +4597,242 @@
         <v>33</v>
       </c>
       <c r="E184" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G184" t="s">
         <v>26</v>
       </c>
       <c r="H184" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B185">
-        <v>1.7</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="C185" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E185" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G185" t="s">
         <v>26</v>
       </c>
       <c r="H185" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="B186">
-        <v>0.81499999999999995</v>
+        <v>0.151</v>
       </c>
       <c r="C186" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D186" t="s">
         <v>33</v>
       </c>
       <c r="E186" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G186" t="s">
         <v>26</v>
       </c>
       <c r="H186" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="B187">
-        <v>-5.5099999999999998E-5</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C187" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G187" t="s">
         <v>26</v>
       </c>
       <c r="H187" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>64</v>
-      </c>
-      <c r="B188">
-        <v>0.25</v>
-      </c>
-      <c r="C188" t="s">
-        <v>25</v>
-      </c>
-      <c r="D188" t="s">
-        <v>33</v>
-      </c>
-      <c r="E188" t="s">
-        <v>65</v>
-      </c>
-      <c r="G188" t="s">
-        <v>26</v>
-      </c>
-      <c r="H188" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>121</v>
-      </c>
-      <c r="B189">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="C189" t="s">
-        <v>25</v>
-      </c>
-      <c r="D189" t="s">
-        <v>33</v>
-      </c>
-      <c r="E189" t="s">
-        <v>65</v>
-      </c>
-      <c r="G189" t="s">
-        <v>26</v>
-      </c>
-      <c r="H189" t="s">
-        <v>67</v>
+      <c r="A189" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>122</v>
-      </c>
-      <c r="B190">
-        <v>0.151</v>
-      </c>
-      <c r="C190" t="s">
-        <v>25</v>
-      </c>
-      <c r="D190" t="s">
-        <v>33</v>
-      </c>
-      <c r="E190" t="s">
-        <v>65</v>
-      </c>
-      <c r="G190" t="s">
-        <v>26</v>
-      </c>
-      <c r="H190" t="s">
-        <v>123</v>
+        <v>3</v>
+      </c>
+      <c r="B190" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>124</v>
-      </c>
-      <c r="B191">
-        <v>0.84099999999999997</v>
-      </c>
-      <c r="C191" t="s">
-        <v>25</v>
-      </c>
-      <c r="D191" t="s">
-        <v>6</v>
-      </c>
-      <c r="E191" t="s">
-        <v>65</v>
-      </c>
-      <c r="G191" t="s">
-        <v>26</v>
-      </c>
-      <c r="H191" t="s">
-        <v>125</v>
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>39</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A193" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>118</v>
+      <c r="A193" t="s">
+        <v>7</v>
+      </c>
+      <c r="B193" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>3</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>185</v>
+        <v>8</v>
+      </c>
+      <c r="B194" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B195" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A197" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H197" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B196" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
-        <v>8</v>
-      </c>
-      <c r="B197" t="s">
-        <v>9</v>
-      </c>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+      <c r="M197" s="2"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>10</v>
-      </c>
-      <c r="B198" t="s">
-        <v>11</v>
+        <v>43</v>
+      </c>
+      <c r="B198">
+        <v>2.6</v>
+      </c>
+      <c r="C198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" t="s">
+        <v>111</v>
+      </c>
+      <c r="G198" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="B199">
+        <v>1.2E-4</v>
+      </c>
+      <c r="C199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" t="s">
+        <v>19</v>
+      </c>
+      <c r="G199" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A200" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2"/>
-      <c r="L200" s="2"/>
-      <c r="M200" s="2"/>
+      <c r="A200" t="s">
+        <v>112</v>
+      </c>
+      <c r="B200">
+        <v>1.46E-6</v>
+      </c>
+      <c r="C200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" t="s">
+        <v>19</v>
+      </c>
+      <c r="G200" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B201">
-        <v>2.0100000000000001E-3</v>
+        <v>4.5800000000000002E-4</v>
       </c>
       <c r="C201" t="s">
         <v>18</v>
@@ -4847,10 +4849,10 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B202">
-        <v>1.43</v>
+        <v>2.2399999999999998E-3</v>
       </c>
       <c r="C202" t="s">
         <v>18</v>
@@ -4859,7 +4861,7 @@
         <v>11</v>
       </c>
       <c r="F202" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="G202" t="s">
         <v>20</v>
@@ -4867,19 +4869,19 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B203">
-        <v>4.8500000000000002E-6</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="C203" t="s">
         <v>18</v>
       </c>
       <c r="E203" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F203" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="G203" t="s">
         <v>20</v>
@@ -4887,16 +4889,16 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B204">
-        <v>1.06E-3</v>
+        <v>4.7699999999999999E-2</v>
       </c>
       <c r="C204" t="s">
         <v>18</v>
       </c>
       <c r="E204" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F204" t="s">
         <v>19</v>
@@ -4907,19 +4909,19 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B205">
-        <v>8.6399999999999997E-4</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
       </c>
       <c r="E205" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F205" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G205" t="s">
         <v>20</v>
@@ -4927,159 +4929,177 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="B206">
-        <v>1.15E-7</v>
+        <v>1</v>
       </c>
       <c r="C206" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D206" t="s">
+        <v>6</v>
       </c>
       <c r="E206" t="s">
         <v>11</v>
       </c>
-      <c r="F206" t="s">
-        <v>47</v>
-      </c>
       <c r="G206" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="H206" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="B207">
-        <v>1.5099999999999999E-5</v>
+        <v>5.5099999999999998E-5</v>
       </c>
       <c r="C207" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D207" t="s">
+        <v>6</v>
       </c>
       <c r="E207" t="s">
         <v>11</v>
       </c>
-      <c r="F207" t="s">
-        <v>47</v>
-      </c>
       <c r="G207" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H207" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="B208">
-        <v>1E-3</v>
+        <v>0.92</v>
       </c>
       <c r="C208" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D208" t="s">
+        <v>33</v>
       </c>
       <c r="E208" t="s">
         <v>11</v>
       </c>
-      <c r="F208" t="s">
-        <v>19</v>
-      </c>
       <c r="G208" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H208" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>50</v>
-      </c>
-      <c r="B209">
-        <v>0.14899999999999999</v>
+        <v>51</v>
+      </c>
+      <c r="B209" s="1">
+        <v>3.29E-10</v>
       </c>
       <c r="C209" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D209" t="s">
+        <v>6</v>
       </c>
       <c r="E209" t="s">
-        <v>41</v>
-      </c>
-      <c r="F209" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G209" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H209" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B210">
-        <v>0.42199999999999999</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D210" t="s">
+        <v>33</v>
       </c>
       <c r="E210" t="s">
-        <v>41</v>
-      </c>
-      <c r="F210" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G210" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H210" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="B211">
-        <v>0.56200000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="C211" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D211" t="s">
+        <v>38</v>
       </c>
       <c r="E211" t="s">
-        <v>41</v>
-      </c>
-      <c r="F211" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G211" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H211" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="C212" t="s">
         <v>22</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
       </c>
       <c r="G212" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H212" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>186</v>
+        <v>62</v>
       </c>
       <c r="B213">
-        <v>3.2499999999999999E-4</v>
+        <v>-5.5099999999999998E-5</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -5088,61 +5108,61 @@
         <v>26</v>
       </c>
       <c r="H213" t="s">
-        <v>187</v>
+        <v>63</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>51</v>
-      </c>
-      <c r="B214" s="1">
-        <v>4.0000000000000001E-10</v>
+        <v>64</v>
+      </c>
+      <c r="B214">
+        <v>0.25</v>
       </c>
       <c r="C214" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E214" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G214" t="s">
         <v>26</v>
       </c>
       <c r="H214" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B215">
-        <v>0.747</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="C215" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="E215" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G215" t="s">
         <v>26</v>
       </c>
       <c r="H215" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="B216">
-        <v>0.82599999999999996</v>
+        <v>0.151</v>
       </c>
       <c r="C216" t="s">
         <v>25</v>
@@ -5151,318 +5171,294 @@
         <v>33</v>
       </c>
       <c r="E216" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G216" t="s">
         <v>26</v>
       </c>
       <c r="H216" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="B217">
-        <v>-1.56E-4</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C217" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E217" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G217" t="s">
         <v>26</v>
       </c>
       <c r="H217" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>55</v>
-      </c>
-      <c r="B218">
-        <v>9.1900000000000003E-3</v>
-      </c>
-      <c r="C218" t="s">
-        <v>25</v>
-      </c>
-      <c r="D218" t="s">
-        <v>33</v>
-      </c>
-      <c r="E218" t="s">
-        <v>11</v>
-      </c>
-      <c r="G218" t="s">
-        <v>26</v>
-      </c>
-      <c r="H218" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A219" t="s">
-        <v>57</v>
-      </c>
-      <c r="B219">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="C219" t="s">
-        <v>25</v>
-      </c>
-      <c r="D219" t="s">
-        <v>6</v>
-      </c>
-      <c r="E219" t="s">
-        <v>58</v>
-      </c>
-      <c r="G219" t="s">
-        <v>26</v>
-      </c>
-      <c r="H219" t="s">
-        <v>59</v>
+      <c r="A219" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>160</v>
-      </c>
-      <c r="B220">
-        <v>26.3</v>
-      </c>
-      <c r="C220" t="s">
-        <v>22</v>
-      </c>
-      <c r="D220" t="s">
-        <v>6</v>
-      </c>
-      <c r="E220" t="s">
-        <v>61</v>
-      </c>
-      <c r="G220" t="s">
-        <v>26</v>
-      </c>
-      <c r="H220" t="s">
-        <v>160</v>
+        <v>3</v>
+      </c>
+      <c r="B220" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>62</v>
-      </c>
-      <c r="B221">
-        <v>-3.2499999999999999E-4</v>
-      </c>
-      <c r="C221" t="s">
-        <v>25</v>
-      </c>
-      <c r="D221" t="s">
-        <v>33</v>
-      </c>
-      <c r="E221" t="s">
-        <v>11</v>
-      </c>
-      <c r="G221" t="s">
-        <v>26</v>
-      </c>
-      <c r="H221" t="s">
-        <v>63</v>
+        <v>5</v>
+      </c>
+      <c r="B221" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>64</v>
-      </c>
-      <c r="B222">
-        <v>0.25</v>
-      </c>
-      <c r="C222" t="s">
-        <v>25</v>
-      </c>
-      <c r="D222" t="s">
-        <v>33</v>
-      </c>
-      <c r="E222" t="s">
-        <v>65</v>
-      </c>
-      <c r="G222" t="s">
-        <v>26</v>
-      </c>
-      <c r="H222" t="s">
-        <v>66</v>
+        <v>7</v>
+      </c>
+      <c r="B222" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>121</v>
-      </c>
-      <c r="B223">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="C223" t="s">
-        <v>25</v>
-      </c>
-      <c r="D223" t="s">
-        <v>33</v>
-      </c>
-      <c r="E223" t="s">
-        <v>65</v>
-      </c>
-      <c r="G223" t="s">
-        <v>26</v>
-      </c>
-      <c r="H223" t="s">
-        <v>67</v>
+        <v>8</v>
+      </c>
+      <c r="B223" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>122</v>
-      </c>
-      <c r="B224">
-        <v>0.151</v>
-      </c>
-      <c r="C224" t="s">
-        <v>25</v>
-      </c>
-      <c r="D224" t="s">
-        <v>33</v>
-      </c>
-      <c r="E224" t="s">
-        <v>65</v>
-      </c>
-      <c r="G224" t="s">
-        <v>26</v>
-      </c>
-      <c r="H224" t="s">
-        <v>123</v>
+        <v>10</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>124</v>
-      </c>
-      <c r="B225">
-        <v>0.84099999999999997</v>
-      </c>
-      <c r="C225" t="s">
-        <v>25</v>
-      </c>
-      <c r="D225" t="s">
-        <v>6</v>
-      </c>
-      <c r="E225" t="s">
-        <v>65</v>
-      </c>
-      <c r="G225" t="s">
-        <v>26</v>
-      </c>
-      <c r="H225" t="s">
-        <v>125</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I226" s="2"/>
+      <c r="J226" s="2"/>
+      <c r="K226" s="2"/>
+      <c r="L226" s="2"/>
+      <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A227" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>164</v>
+      <c r="A227" t="s">
+        <v>17</v>
+      </c>
+      <c r="B227">
+        <v>2.0100000000000001E-3</v>
+      </c>
+      <c r="C227" t="s">
+        <v>18</v>
+      </c>
+      <c r="E227" t="s">
+        <v>11</v>
+      </c>
+      <c r="F227" t="s">
+        <v>19</v>
+      </c>
+      <c r="G227" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>3</v>
-      </c>
-      <c r="B228" t="s">
-        <v>188</v>
+        <v>43</v>
+      </c>
+      <c r="B228">
+        <v>1.43</v>
+      </c>
+      <c r="C228" t="s">
+        <v>18</v>
+      </c>
+      <c r="E228" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" t="s">
+        <v>19</v>
+      </c>
+      <c r="G228" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>5</v>
-      </c>
-      <c r="B229" t="s">
-        <v>6</v>
+        <v>44</v>
+      </c>
+      <c r="B229">
+        <v>4.8500000000000002E-6</v>
+      </c>
+      <c r="C229" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" t="s">
+        <v>19</v>
+      </c>
+      <c r="G229" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>7</v>
-      </c>
-      <c r="B230" t="s">
-        <v>107</v>
+        <v>45</v>
+      </c>
+      <c r="B230">
+        <v>1.06E-3</v>
+      </c>
+      <c r="C230" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230" t="s">
+        <v>11</v>
+      </c>
+      <c r="F230" t="s">
+        <v>19</v>
+      </c>
+      <c r="G230" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>8</v>
-      </c>
-      <c r="B231" t="s">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="B231">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>18</v>
+      </c>
+      <c r="E231" t="s">
+        <v>11</v>
+      </c>
+      <c r="F231" t="s">
+        <v>19</v>
+      </c>
+      <c r="G231" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>10</v>
-      </c>
-      <c r="B232" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="B232">
+        <v>1.15E-7</v>
+      </c>
+      <c r="C232" t="s">
+        <v>18</v>
+      </c>
+      <c r="E232" t="s">
+        <v>11</v>
+      </c>
+      <c r="F232" t="s">
+        <v>47</v>
+      </c>
+      <c r="G232" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>12</v>
+        <v>48</v>
+      </c>
+      <c r="B233">
+        <v>1.5099999999999999E-5</v>
+      </c>
+      <c r="C233" t="s">
+        <v>18</v>
+      </c>
+      <c r="E233" t="s">
+        <v>11</v>
+      </c>
+      <c r="F233" t="s">
+        <v>47</v>
+      </c>
+      <c r="G233" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A234" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I234" s="2"/>
-      <c r="J234" s="2"/>
-      <c r="K234" s="2"/>
-      <c r="L234" s="2"/>
-      <c r="M234" s="2"/>
+      <c r="A234" t="s">
+        <v>49</v>
+      </c>
+      <c r="B234">
+        <v>1E-3</v>
+      </c>
+      <c r="C234" t="s">
+        <v>18</v>
+      </c>
+      <c r="E234" t="s">
+        <v>11</v>
+      </c>
+      <c r="F234" t="s">
+        <v>19</v>
+      </c>
+      <c r="G234" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B235">
-        <v>2.0100000000000001E-3</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="C235" t="s">
         <v>18</v>
       </c>
       <c r="E235" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -5473,19 +5469,19 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B236">
-        <v>0.26</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="C236" t="s">
         <v>18</v>
       </c>
       <c r="E236" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F236" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G236" t="s">
         <v>20</v>
@@ -5493,19 +5489,19 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>44</v>
-      </c>
-      <c r="B237" s="1">
-        <v>7.7599999999999999E-16</v>
+        <v>40</v>
+      </c>
+      <c r="B237">
+        <v>0.56200000000000006</v>
       </c>
       <c r="C237" t="s">
         <v>18</v>
       </c>
       <c r="E237" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F237" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G237" t="s">
         <v>20</v>
@@ -5513,170 +5509,194 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="B238">
-        <v>7.36E-4</v>
+        <v>1</v>
       </c>
       <c r="C238" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D238" t="s">
+        <v>6</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
       </c>
-      <c r="F238" t="s">
-        <v>19</v>
-      </c>
       <c r="G238" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="H238" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="B239">
-        <v>8.6200000000000003E-4</v>
+        <v>3.2499999999999999E-4</v>
       </c>
       <c r="C239" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D239" t="s">
+        <v>6</v>
       </c>
       <c r="E239" t="s">
         <v>11</v>
       </c>
-      <c r="F239" t="s">
-        <v>19</v>
-      </c>
       <c r="G239" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H239" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>21</v>
-      </c>
-      <c r="B240">
-        <v>1.15E-7</v>
+        <v>51</v>
+      </c>
+      <c r="B240" s="1">
+        <v>4.0000000000000001E-10</v>
       </c>
       <c r="C240" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D240" t="s">
+        <v>6</v>
       </c>
       <c r="E240" t="s">
-        <v>11</v>
-      </c>
-      <c r="F240" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="G240" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H240" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B241">
-        <v>1.5099999999999999E-5</v>
+        <v>0.747</v>
       </c>
       <c r="C241" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D241" t="s">
+        <v>120</v>
       </c>
       <c r="E241" t="s">
-        <v>11</v>
-      </c>
-      <c r="F241" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G241" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H241" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B242">
-        <v>1E-3</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="C242" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D242" t="s">
+        <v>33</v>
       </c>
       <c r="E242" t="s">
         <v>11</v>
       </c>
-      <c r="F242" t="s">
-        <v>19</v>
-      </c>
       <c r="G242" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H242" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B243">
-        <v>0.153</v>
+        <v>-1.56E-4</v>
       </c>
       <c r="C243" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D243" t="s">
+        <v>33</v>
       </c>
       <c r="E243" t="s">
         <v>41</v>
       </c>
-      <c r="F243" t="s">
-        <v>19</v>
-      </c>
       <c r="G243" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H243" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B244">
-        <v>0.41899999999999998</v>
+        <v>9.1900000000000003E-3</v>
       </c>
       <c r="C244" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D244" t="s">
+        <v>33</v>
       </c>
       <c r="E244" t="s">
-        <v>41</v>
-      </c>
-      <c r="F244" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G244" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H244" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B245">
-        <v>0.57199999999999995</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="C245" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D245" t="s">
+        <v>6</v>
       </c>
       <c r="E245" t="s">
-        <v>41</v>
-      </c>
-      <c r="F245" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G245" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H245" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B246">
-        <v>1</v>
+        <v>26.3</v>
       </c>
       <c r="C246" t="s">
         <v>22</v>
@@ -5685,27 +5705,27 @@
         <v>6</v>
       </c>
       <c r="E246" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G246" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H246" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="B247">
-        <v>1.17</v>
+        <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C247" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E247" t="s">
         <v>11</v>
@@ -5714,430 +5734,400 @@
         <v>26</v>
       </c>
       <c r="H247" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="B248">
-        <v>3.2499999999999999E-4</v>
+        <v>0.25</v>
       </c>
       <c r="C248" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E248" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G248" t="s">
         <v>26</v>
       </c>
       <c r="H248" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>51</v>
-      </c>
-      <c r="B249" s="1">
-        <v>4.0000000000000001E-10</v>
+        <v>121</v>
+      </c>
+      <c r="B249">
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="C249" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E249" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G249" t="s">
         <v>26</v>
       </c>
       <c r="H249" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B250">
-        <v>0.747</v>
+        <v>0.151</v>
       </c>
       <c r="C250" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="E250" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G250" t="s">
         <v>26</v>
       </c>
       <c r="H250" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="B251">
-        <v>0.82599999999999996</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C251" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E251" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G251" t="s">
         <v>26</v>
       </c>
       <c r="H251" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A252" t="s">
-        <v>53</v>
-      </c>
-      <c r="B252">
-        <v>-1.56E-4</v>
-      </c>
-      <c r="C252" t="s">
-        <v>25</v>
-      </c>
-      <c r="D252" t="s">
-        <v>33</v>
-      </c>
-      <c r="E252" t="s">
-        <v>41</v>
-      </c>
-      <c r="G252" t="s">
-        <v>26</v>
-      </c>
-      <c r="H252" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A253" t="s">
-        <v>55</v>
-      </c>
-      <c r="B253">
-        <v>9.2099999999999994E-3</v>
-      </c>
-      <c r="C253" t="s">
-        <v>25</v>
-      </c>
-      <c r="D253" t="s">
-        <v>33</v>
-      </c>
-      <c r="E253" t="s">
-        <v>11</v>
-      </c>
-      <c r="G253" t="s">
-        <v>26</v>
-      </c>
-      <c r="H253" t="s">
-        <v>56</v>
+      <c r="A253" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>57</v>
-      </c>
-      <c r="B254">
-        <v>0.95699999999999996</v>
-      </c>
-      <c r="C254" t="s">
-        <v>25</v>
-      </c>
-      <c r="D254" t="s">
-        <v>6</v>
-      </c>
-      <c r="E254" t="s">
-        <v>58</v>
-      </c>
-      <c r="G254" t="s">
-        <v>26</v>
-      </c>
-      <c r="H254" t="s">
-        <v>59</v>
+        <v>3</v>
+      </c>
+      <c r="B254" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>160</v>
-      </c>
-      <c r="B255">
-        <v>26.3</v>
-      </c>
-      <c r="C255" t="s">
-        <v>22</v>
-      </c>
-      <c r="D255" t="s">
-        <v>6</v>
-      </c>
-      <c r="E255" t="s">
-        <v>61</v>
-      </c>
-      <c r="G255" t="s">
-        <v>26</v>
-      </c>
-      <c r="H255" t="s">
-        <v>160</v>
+        <v>5</v>
+      </c>
+      <c r="B255" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>171</v>
-      </c>
-      <c r="B256">
-        <v>1.17</v>
-      </c>
-      <c r="C256" t="s">
-        <v>22</v>
-      </c>
-      <c r="D256" t="s">
-        <v>6</v>
-      </c>
-      <c r="E256" t="s">
-        <v>11</v>
-      </c>
-      <c r="G256" t="s">
-        <v>26</v>
-      </c>
-      <c r="H256" t="s">
-        <v>171</v>
+        <v>7</v>
+      </c>
+      <c r="B256" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>62</v>
-      </c>
-      <c r="B257">
-        <v>-3.2499999999999999E-4</v>
-      </c>
-      <c r="C257" t="s">
-        <v>25</v>
-      </c>
-      <c r="D257" t="s">
-        <v>33</v>
-      </c>
-      <c r="E257" t="s">
-        <v>11</v>
-      </c>
-      <c r="G257" t="s">
-        <v>26</v>
-      </c>
-      <c r="H257" t="s">
-        <v>63</v>
+        <v>8</v>
+      </c>
+      <c r="B257" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>64</v>
-      </c>
-      <c r="B258">
-        <v>0.25</v>
-      </c>
-      <c r="C258" t="s">
-        <v>25</v>
-      </c>
-      <c r="D258" t="s">
-        <v>33</v>
-      </c>
-      <c r="E258" t="s">
-        <v>65</v>
-      </c>
-      <c r="G258" t="s">
-        <v>26</v>
-      </c>
-      <c r="H258" t="s">
-        <v>66</v>
+        <v>10</v>
+      </c>
+      <c r="B258" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>121</v>
-      </c>
-      <c r="B259">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="C259" t="s">
-        <v>25</v>
-      </c>
-      <c r="D259" t="s">
-        <v>33</v>
-      </c>
-      <c r="E259" t="s">
-        <v>65</v>
-      </c>
-      <c r="G259" t="s">
-        <v>26</v>
-      </c>
-      <c r="H259" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A260" t="s">
-        <v>122</v>
-      </c>
-      <c r="B260">
-        <v>0.151</v>
-      </c>
-      <c r="C260" t="s">
-        <v>25</v>
-      </c>
-      <c r="D260" t="s">
-        <v>33</v>
-      </c>
-      <c r="E260" t="s">
-        <v>65</v>
-      </c>
-      <c r="G260" t="s">
-        <v>26</v>
-      </c>
-      <c r="H260" t="s">
-        <v>123</v>
-      </c>
+      <c r="A260" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I260" s="2"/>
+      <c r="J260" s="2"/>
+      <c r="K260" s="2"/>
+      <c r="L260" s="2"/>
+      <c r="M260" s="2"/>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="B261">
-        <v>0.84099999999999997</v>
+        <v>2.0100000000000001E-3</v>
       </c>
       <c r="C261" t="s">
-        <v>25</v>
-      </c>
-      <c r="D261" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E261" t="s">
-        <v>65</v>
+        <v>11</v>
+      </c>
+      <c r="F261" t="s">
+        <v>19</v>
       </c>
       <c r="G261" t="s">
-        <v>26</v>
-      </c>
-      <c r="H261" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>43</v>
+      </c>
+      <c r="B262">
+        <v>0.26</v>
+      </c>
+      <c r="C262" t="s">
+        <v>18</v>
+      </c>
+      <c r="E262" t="s">
+        <v>11</v>
+      </c>
+      <c r="F262" t="s">
+        <v>19</v>
+      </c>
+      <c r="G262" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A263" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>165</v>
+      <c r="A263" t="s">
+        <v>44</v>
+      </c>
+      <c r="B263" s="1">
+        <v>7.7599999999999999E-16</v>
+      </c>
+      <c r="C263" t="s">
+        <v>18</v>
+      </c>
+      <c r="E263" t="s">
+        <v>11</v>
+      </c>
+      <c r="F263" t="s">
+        <v>19</v>
+      </c>
+      <c r="G263" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>3</v>
-      </c>
-      <c r="B264" t="s">
-        <v>189</v>
+        <v>45</v>
+      </c>
+      <c r="B264">
+        <v>7.36E-4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>18</v>
+      </c>
+      <c r="E264" t="s">
+        <v>11</v>
+      </c>
+      <c r="F264" t="s">
+        <v>19</v>
+      </c>
+      <c r="G264" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>5</v>
-      </c>
-      <c r="B265" t="s">
-        <v>6</v>
+        <v>46</v>
+      </c>
+      <c r="B265">
+        <v>8.6200000000000003E-4</v>
+      </c>
+      <c r="C265" t="s">
+        <v>18</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
+      </c>
+      <c r="F265" t="s">
+        <v>19</v>
+      </c>
+      <c r="G265" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>7</v>
-      </c>
-      <c r="B266" t="s">
-        <v>107</v>
+        <v>21</v>
+      </c>
+      <c r="B266">
+        <v>1.15E-7</v>
+      </c>
+      <c r="C266" t="s">
+        <v>18</v>
+      </c>
+      <c r="E266" t="s">
+        <v>11</v>
+      </c>
+      <c r="F266" t="s">
+        <v>47</v>
+      </c>
+      <c r="G266" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>8</v>
-      </c>
-      <c r="B267" t="s">
-        <v>9</v>
+        <v>48</v>
+      </c>
+      <c r="B267">
+        <v>1.5099999999999999E-5</v>
+      </c>
+      <c r="C267" t="s">
+        <v>18</v>
+      </c>
+      <c r="E267" t="s">
+        <v>11</v>
+      </c>
+      <c r="F267" t="s">
+        <v>47</v>
+      </c>
+      <c r="G267" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>10</v>
-      </c>
-      <c r="B268" t="s">
-        <v>11</v>
+        <v>49</v>
+      </c>
+      <c r="B268">
+        <v>1E-3</v>
+      </c>
+      <c r="C268" t="s">
+        <v>18</v>
+      </c>
+      <c r="E268" t="s">
+        <v>11</v>
+      </c>
+      <c r="F268" t="s">
+        <v>19</v>
+      </c>
+      <c r="G268" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>12</v>
+        <v>50</v>
+      </c>
+      <c r="B269">
+        <v>0.153</v>
+      </c>
+      <c r="C269" t="s">
+        <v>18</v>
+      </c>
+      <c r="E269" t="s">
+        <v>41</v>
+      </c>
+      <c r="F269" t="s">
+        <v>19</v>
+      </c>
+      <c r="G269" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A270" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I270" s="2"/>
-      <c r="J270" s="2"/>
-      <c r="K270" s="2"/>
-      <c r="L270" s="2"/>
-      <c r="M270" s="2"/>
+      <c r="A270" t="s">
+        <v>50</v>
+      </c>
+      <c r="B270">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="C270" t="s">
+        <v>18</v>
+      </c>
+      <c r="E270" t="s">
+        <v>41</v>
+      </c>
+      <c r="F270" t="s">
+        <v>47</v>
+      </c>
+      <c r="G270" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B271">
-        <v>2.0100000000000001E-3</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="C271" t="s">
         <v>18</v>
       </c>
       <c r="E271" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F271" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G271" t="s">
         <v>20</v>
@@ -6145,210 +6135,240 @@
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="B272">
-        <v>2.6499999999999999E-2</v>
+        <v>1</v>
       </c>
       <c r="C272" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D272" t="s">
+        <v>6</v>
       </c>
       <c r="E272" t="s">
         <v>11</v>
       </c>
-      <c r="F272" t="s">
-        <v>19</v>
-      </c>
       <c r="G272" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="H272" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>44</v>
-      </c>
-      <c r="B273" s="1">
-        <v>7.7599999999999999E-16</v>
+        <v>173</v>
+      </c>
+      <c r="B273">
+        <v>1.17</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D273" t="s">
+        <v>6</v>
       </c>
       <c r="E273" t="s">
         <v>11</v>
       </c>
-      <c r="F273" t="s">
-        <v>19</v>
-      </c>
       <c r="G273" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H273" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="B274">
-        <v>7.36E-4</v>
+        <v>3.2499999999999999E-4</v>
       </c>
       <c r="C274" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D274" t="s">
+        <v>6</v>
       </c>
       <c r="E274" t="s">
         <v>11</v>
       </c>
-      <c r="F274" t="s">
-        <v>19</v>
-      </c>
       <c r="G274" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H274" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>46</v>
-      </c>
-      <c r="B275">
-        <v>8.61E-4</v>
+        <v>51</v>
+      </c>
+      <c r="B275" s="1">
+        <v>4.0000000000000001E-10</v>
       </c>
       <c r="C275" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D275" t="s">
+        <v>6</v>
       </c>
       <c r="E275" t="s">
-        <v>11</v>
-      </c>
-      <c r="F275" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G275" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H275" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="B276">
-        <v>1.15E-7</v>
+        <v>0.747</v>
       </c>
       <c r="C276" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D276" t="s">
+        <v>120</v>
       </c>
       <c r="E276" t="s">
-        <v>11</v>
-      </c>
-      <c r="F276" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G276" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H276" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B277">
-        <v>1.5099999999999999E-5</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="C277" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D277" t="s">
+        <v>33</v>
       </c>
       <c r="E277" t="s">
         <v>11</v>
       </c>
-      <c r="F277" t="s">
-        <v>47</v>
-      </c>
       <c r="G277" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H277" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B278">
-        <v>1E-3</v>
+        <v>-1.56E-4</v>
       </c>
       <c r="C278" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D278" t="s">
+        <v>33</v>
       </c>
       <c r="E278" t="s">
-        <v>11</v>
-      </c>
-      <c r="F278" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G278" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H278" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B279">
-        <v>0.153</v>
+        <v>9.2099999999999994E-3</v>
       </c>
       <c r="C279" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D279" t="s">
+        <v>33</v>
       </c>
       <c r="E279" t="s">
-        <v>41</v>
-      </c>
-      <c r="F279" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G279" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H279" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B280">
-        <v>0.41899999999999998</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="C280" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D280" t="s">
+        <v>6</v>
       </c>
       <c r="E280" t="s">
-        <v>41</v>
-      </c>
-      <c r="F280" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G280" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H280" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="B281">
-        <v>0.57199999999999995</v>
+        <v>26.3</v>
       </c>
       <c r="C281" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D281" t="s">
+        <v>6</v>
       </c>
       <c r="E281" t="s">
-        <v>41</v>
-      </c>
-      <c r="F281" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="G281" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="H281" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B282">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="C282" t="s">
         <v>22</v>
@@ -6360,24 +6380,24 @@
         <v>11</v>
       </c>
       <c r="G282" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H282" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="B283">
-        <v>1.41</v>
+        <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C283" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E283" t="s">
         <v>11</v>
@@ -6386,439 +6406,408 @@
         <v>26</v>
       </c>
       <c r="H283" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="B284">
-        <v>3.2499999999999999E-4</v>
+        <v>0.25</v>
       </c>
       <c r="C284" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E284" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G284" t="s">
         <v>26</v>
       </c>
       <c r="H284" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="B285">
-        <v>0.95299999999999996</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="C285" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E285" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G285" t="s">
         <v>26</v>
       </c>
       <c r="H285" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>51</v>
-      </c>
-      <c r="B286" s="1">
-        <v>4.0000000000000001E-10</v>
+        <v>122</v>
+      </c>
+      <c r="B286">
+        <v>0.151</v>
       </c>
       <c r="C286" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E286" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G286" t="s">
         <v>26</v>
       </c>
       <c r="H286" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B287">
-        <v>0.747</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="C287" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E287" t="s">
+        <v>65</v>
+      </c>
+      <c r="G287" t="s">
+        <v>26</v>
+      </c>
+      <c r="H287" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A289" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>3</v>
+      </c>
+      <c r="B290" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>5</v>
+      </c>
+      <c r="B291" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>7</v>
+      </c>
+      <c r="B292" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>8</v>
+      </c>
+      <c r="B293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>10</v>
+      </c>
+      <c r="B294" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A296" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H296" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I296" s="2"/>
+      <c r="J296" s="2"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="2"/>
+      <c r="M296" s="2"/>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>17</v>
+      </c>
+      <c r="B297">
+        <v>2.0100000000000001E-3</v>
+      </c>
+      <c r="C297" t="s">
+        <v>18</v>
+      </c>
+      <c r="E297" t="s">
+        <v>11</v>
+      </c>
+      <c r="F297" t="s">
+        <v>19</v>
+      </c>
+      <c r="G297" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>43</v>
+      </c>
+      <c r="B298">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="C298" t="s">
+        <v>18</v>
+      </c>
+      <c r="E298" t="s">
+        <v>11</v>
+      </c>
+      <c r="F298" t="s">
+        <v>19</v>
+      </c>
+      <c r="G298" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>44</v>
+      </c>
+      <c r="B299" s="1">
+        <v>7.7599999999999999E-16</v>
+      </c>
+      <c r="C299" t="s">
+        <v>18</v>
+      </c>
+      <c r="E299" t="s">
+        <v>11</v>
+      </c>
+      <c r="F299" t="s">
+        <v>19</v>
+      </c>
+      <c r="G299" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>45</v>
+      </c>
+      <c r="B300">
+        <v>7.36E-4</v>
+      </c>
+      <c r="C300" t="s">
+        <v>18</v>
+      </c>
+      <c r="E300" t="s">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>19</v>
+      </c>
+      <c r="G300" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>46</v>
+      </c>
+      <c r="B301">
+        <v>8.61E-4</v>
+      </c>
+      <c r="C301" t="s">
+        <v>18</v>
+      </c>
+      <c r="E301" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" t="s">
+        <v>19</v>
+      </c>
+      <c r="G301" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>21</v>
+      </c>
+      <c r="B302">
+        <v>1.15E-7</v>
+      </c>
+      <c r="C302" t="s">
+        <v>18</v>
+      </c>
+      <c r="E302" t="s">
+        <v>11</v>
+      </c>
+      <c r="F302" t="s">
+        <v>47</v>
+      </c>
+      <c r="G302" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>48</v>
+      </c>
+      <c r="B303">
+        <v>1.5099999999999999E-5</v>
+      </c>
+      <c r="C303" t="s">
+        <v>18</v>
+      </c>
+      <c r="E303" t="s">
+        <v>11</v>
+      </c>
+      <c r="F303" t="s">
+        <v>47</v>
+      </c>
+      <c r="G303" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>49</v>
+      </c>
+      <c r="B304">
+        <v>1E-3</v>
+      </c>
+      <c r="C304" t="s">
+        <v>18</v>
+      </c>
+      <c r="E304" t="s">
+        <v>11</v>
+      </c>
+      <c r="F304" t="s">
+        <v>19</v>
+      </c>
+      <c r="G304" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>50</v>
+      </c>
+      <c r="B305">
+        <v>0.153</v>
+      </c>
+      <c r="C305" t="s">
+        <v>18</v>
+      </c>
+      <c r="E305" t="s">
         <v>41</v>
       </c>
-      <c r="G287" t="s">
-        <v>26</v>
-      </c>
-      <c r="H287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
-        <v>32</v>
-      </c>
-      <c r="B288">
-        <v>0.82599999999999996</v>
-      </c>
-      <c r="C288" t="s">
-        <v>25</v>
-      </c>
-      <c r="D288" t="s">
-        <v>33</v>
-      </c>
-      <c r="E288" t="s">
-        <v>11</v>
-      </c>
-      <c r="G288" t="s">
-        <v>26</v>
-      </c>
-      <c r="H288" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A289" t="s">
-        <v>53</v>
-      </c>
-      <c r="B289">
-        <v>-1.56E-4</v>
-      </c>
-      <c r="C289" t="s">
-        <v>25</v>
-      </c>
-      <c r="D289" t="s">
-        <v>33</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F305" t="s">
+        <v>19</v>
+      </c>
+      <c r="G305" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>50</v>
+      </c>
+      <c r="B306">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="C306" t="s">
+        <v>18</v>
+      </c>
+      <c r="E306" t="s">
         <v>41</v>
       </c>
-      <c r="G289" t="s">
-        <v>26</v>
-      </c>
-      <c r="H289" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A290" t="s">
-        <v>55</v>
-      </c>
-      <c r="B290">
-        <v>9.2099999999999994E-3</v>
-      </c>
-      <c r="C290" t="s">
-        <v>25</v>
-      </c>
-      <c r="D290" t="s">
-        <v>33</v>
-      </c>
-      <c r="E290" t="s">
-        <v>11</v>
-      </c>
-      <c r="G290" t="s">
-        <v>26</v>
-      </c>
-      <c r="H290" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A291" t="s">
-        <v>57</v>
-      </c>
-      <c r="B291">
-        <v>0.97</v>
-      </c>
-      <c r="C291" t="s">
-        <v>25</v>
-      </c>
-      <c r="D291" t="s">
-        <v>6</v>
-      </c>
-      <c r="E291" t="s">
-        <v>58</v>
-      </c>
-      <c r="G291" t="s">
-        <v>26</v>
-      </c>
-      <c r="H291" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A292" t="s">
-        <v>160</v>
-      </c>
-      <c r="B292">
-        <v>26.3</v>
-      </c>
-      <c r="C292" t="s">
-        <v>22</v>
-      </c>
-      <c r="D292" t="s">
-        <v>6</v>
-      </c>
-      <c r="E292" t="s">
-        <v>61</v>
-      </c>
-      <c r="G292" t="s">
-        <v>26</v>
-      </c>
-      <c r="H292" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A293" t="s">
-        <v>172</v>
-      </c>
-      <c r="B293">
-        <v>1.41</v>
-      </c>
-      <c r="C293" t="s">
-        <v>22</v>
-      </c>
-      <c r="D293" t="s">
-        <v>6</v>
-      </c>
-      <c r="E293" t="s">
-        <v>11</v>
-      </c>
-      <c r="G293" t="s">
-        <v>26</v>
-      </c>
-      <c r="H293" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A294" t="s">
-        <v>62</v>
-      </c>
-      <c r="B294">
-        <v>-3.2499999999999999E-4</v>
-      </c>
-      <c r="C294" t="s">
-        <v>25</v>
-      </c>
-      <c r="D294" t="s">
-        <v>33</v>
-      </c>
-      <c r="E294" t="s">
-        <v>11</v>
-      </c>
-      <c r="G294" t="s">
-        <v>26</v>
-      </c>
-      <c r="H294" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A295" t="s">
-        <v>64</v>
-      </c>
-      <c r="B295">
-        <v>0.25</v>
-      </c>
-      <c r="C295" t="s">
-        <v>25</v>
-      </c>
-      <c r="D295" t="s">
-        <v>33</v>
-      </c>
-      <c r="E295" t="s">
-        <v>65</v>
-      </c>
-      <c r="G295" t="s">
-        <v>26</v>
-      </c>
-      <c r="H295" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A296" t="s">
-        <v>121</v>
-      </c>
-      <c r="B296">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="C296" t="s">
-        <v>25</v>
-      </c>
-      <c r="D296" t="s">
-        <v>33</v>
-      </c>
-      <c r="E296" t="s">
-        <v>65</v>
-      </c>
-      <c r="G296" t="s">
-        <v>26</v>
-      </c>
-      <c r="H296" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A297" t="s">
-        <v>122</v>
-      </c>
-      <c r="B297">
-        <v>0.151</v>
-      </c>
-      <c r="C297" t="s">
-        <v>25</v>
-      </c>
-      <c r="D297" t="s">
-        <v>33</v>
-      </c>
-      <c r="E297" t="s">
-        <v>65</v>
-      </c>
-      <c r="G297" t="s">
-        <v>26</v>
-      </c>
-      <c r="H297" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A298" t="s">
-        <v>124</v>
-      </c>
-      <c r="B298">
-        <v>0.84099999999999997</v>
-      </c>
-      <c r="C298" t="s">
-        <v>25</v>
-      </c>
-      <c r="D298" t="s">
-        <v>6</v>
-      </c>
-      <c r="E298" t="s">
-        <v>65</v>
-      </c>
-      <c r="G298" t="s">
-        <v>26</v>
-      </c>
-      <c r="H298" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A300" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A301" t="s">
-        <v>3</v>
-      </c>
-      <c r="B301" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A302" t="s">
-        <v>5</v>
-      </c>
-      <c r="B302" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>7</v>
-      </c>
-      <c r="B303" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>8</v>
-      </c>
-      <c r="B304" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>10</v>
-      </c>
-      <c r="B305" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A307" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H307" s="2"/>
-      <c r="I307" s="2"/>
-      <c r="J307" s="2"/>
-      <c r="K307" s="2"/>
-      <c r="L307" s="2"/>
-      <c r="M307" s="2"/>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F306" t="s">
+        <v>47</v>
+      </c>
+      <c r="G306" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>40</v>
+      </c>
+      <c r="B307">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="C307" t="s">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>41</v>
+      </c>
+      <c r="F307" t="s">
+        <v>42</v>
+      </c>
+      <c r="G307" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -6832,203 +6821,203 @@
       <c r="E308" t="s">
         <v>11</v>
       </c>
-      <c r="F308" t="s">
+      <c r="G308" t="s">
         <v>23</v>
       </c>
-      <c r="G308" t="s">
+      <c r="H308" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>173</v>
+      </c>
+      <c r="B309">
+        <v>1.41</v>
+      </c>
+      <c r="C309" t="s">
+        <v>22</v>
+      </c>
+      <c r="D309" t="s">
+        <v>6</v>
+      </c>
+      <c r="E309" t="s">
+        <v>11</v>
+      </c>
+      <c r="G309" t="s">
+        <v>26</v>
+      </c>
+      <c r="H309" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>186</v>
+      </c>
+      <c r="B310">
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>22</v>
+      </c>
+      <c r="D310" t="s">
+        <v>6</v>
+      </c>
+      <c r="E310" t="s">
+        <v>11</v>
+      </c>
+      <c r="G310" t="s">
+        <v>26</v>
+      </c>
+      <c r="H310" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>127</v>
-      </c>
-      <c r="B309">
-        <v>2.1100000000000001E-2</v>
-      </c>
-      <c r="C309" t="s">
-        <v>25</v>
-      </c>
-      <c r="D309" t="s">
-        <v>6</v>
-      </c>
-      <c r="E309" t="s">
-        <v>11</v>
-      </c>
-      <c r="F309" t="s">
-        <v>26</v>
-      </c>
-      <c r="G309" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>129</v>
-      </c>
-      <c r="B310">
-        <v>1.4400000000000001E-3</v>
-      </c>
-      <c r="C310" t="s">
-        <v>25</v>
-      </c>
-      <c r="D310" t="s">
-        <v>6</v>
-      </c>
-      <c r="E310" t="s">
-        <v>11</v>
-      </c>
-      <c r="F310" t="s">
-        <v>26</v>
-      </c>
-      <c r="G310" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="B311">
-        <v>0.11700000000000001</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="C311" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D311" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E311" t="s">
-        <v>11</v>
-      </c>
-      <c r="F311" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="G311" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H311" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>100</v>
-      </c>
-      <c r="B312">
-        <v>5.1000000000000004E-3</v>
+        <v>51</v>
+      </c>
+      <c r="B312" s="1">
+        <v>4.0000000000000001E-10</v>
       </c>
       <c r="C312" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E312" t="s">
-        <v>11</v>
-      </c>
-      <c r="F312" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G312" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H312" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B313">
-        <v>4.2999999999999999E-4</v>
+        <v>0.747</v>
       </c>
       <c r="C313" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="E313" t="s">
-        <v>11</v>
-      </c>
-      <c r="F313" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G313" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H313" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="B314">
-        <v>0.313</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="C314" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E314" t="s">
         <v>11</v>
       </c>
-      <c r="F314" t="s">
-        <v>26</v>
-      </c>
       <c r="G314" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H314" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B315">
-        <v>1.4400000000000001E-3</v>
+        <v>-1.56E-4</v>
       </c>
       <c r="C315" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E315" t="s">
-        <v>11</v>
-      </c>
-      <c r="F315" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G315" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H315" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="B316">
-        <v>3.8100000000000002E-2</v>
+        <v>9.2099999999999994E-3</v>
       </c>
       <c r="C316" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E316" t="s">
         <v>11</v>
       </c>
-      <c r="F316" t="s">
-        <v>26</v>
-      </c>
       <c r="G316" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H316" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B317">
-        <v>0.248</v>
+        <v>0.97</v>
       </c>
       <c r="C317" t="s">
         <v>25</v>
@@ -7037,658 +7026,724 @@
         <v>6</v>
       </c>
       <c r="E317" t="s">
-        <v>11</v>
-      </c>
-      <c r="F317" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G317" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H317" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B318">
-        <v>0.253</v>
+        <v>26.3</v>
       </c>
       <c r="C318" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D318" t="s">
         <v>6</v>
       </c>
       <c r="E318" t="s">
-        <v>11</v>
-      </c>
-      <c r="F318" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="G318" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="H318" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="B319">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="C319" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D319" t="s">
         <v>6</v>
       </c>
       <c r="E319" t="s">
-        <v>58</v>
-      </c>
-      <c r="F319" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G319" t="s">
-        <v>59</v>
+        <v>26</v>
+      </c>
+      <c r="H319" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>62</v>
+      </c>
+      <c r="B320">
+        <v>-3.2499999999999999E-4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>25</v>
+      </c>
+      <c r="D320" t="s">
+        <v>33</v>
+      </c>
+      <c r="E320" t="s">
+        <v>11</v>
+      </c>
+      <c r="G320" t="s">
+        <v>26</v>
+      </c>
+      <c r="H320" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A321" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>160</v>
+      <c r="A321" t="s">
+        <v>64</v>
+      </c>
+      <c r="B321">
+        <v>0.25</v>
+      </c>
+      <c r="C321" t="s">
+        <v>25</v>
+      </c>
+      <c r="D321" t="s">
+        <v>33</v>
+      </c>
+      <c r="E321" t="s">
+        <v>65</v>
+      </c>
+      <c r="G321" t="s">
+        <v>26</v>
+      </c>
+      <c r="H321" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>3</v>
-      </c>
-      <c r="B322" t="s">
-        <v>4</v>
+        <v>121</v>
+      </c>
+      <c r="B322">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="C322" t="s">
+        <v>25</v>
+      </c>
+      <c r="D322" t="s">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>65</v>
+      </c>
+      <c r="G322" t="s">
+        <v>26</v>
+      </c>
+      <c r="H322" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>5</v>
-      </c>
-      <c r="B323" t="s">
-        <v>6</v>
+        <v>122</v>
+      </c>
+      <c r="B323">
+        <v>0.151</v>
+      </c>
+      <c r="C323" t="s">
+        <v>25</v>
+      </c>
+      <c r="D323" t="s">
+        <v>33</v>
+      </c>
+      <c r="E323" t="s">
+        <v>65</v>
+      </c>
+      <c r="G323" t="s">
+        <v>26</v>
+      </c>
+      <c r="H323" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>7</v>
-      </c>
-      <c r="B324" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A325" t="s">
-        <v>8</v>
-      </c>
-      <c r="B325" t="s">
-        <v>9</v>
+        <v>124</v>
+      </c>
+      <c r="B324">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="C324" t="s">
+        <v>25</v>
+      </c>
+      <c r="D324" t="s">
+        <v>6</v>
+      </c>
+      <c r="E324" t="s">
+        <v>65</v>
+      </c>
+      <c r="G324" t="s">
+        <v>26</v>
+      </c>
+      <c r="H324" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A326" t="s">
-        <v>10</v>
-      </c>
-      <c r="B326" t="s">
-        <v>61</v>
+      <c r="A326" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B327" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A328" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D328" s="2" t="s">
+      <c r="A328" t="s">
         <v>5</v>
       </c>
-      <c r="E328" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G328" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H328" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I328" s="2"/>
-      <c r="J328" s="2"/>
-      <c r="K328" s="2"/>
-      <c r="L328" s="2"/>
-      <c r="M328" s="2"/>
+      <c r="B328" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>142</v>
-      </c>
-      <c r="B329" s="1">
-        <v>1.2E-10</v>
-      </c>
-      <c r="C329" t="s">
-        <v>18</v>
-      </c>
-      <c r="E329" t="s">
-        <v>11</v>
-      </c>
-      <c r="F329" t="s">
-        <v>19</v>
-      </c>
-      <c r="G329" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="B329" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>143</v>
-      </c>
-      <c r="B330" s="1">
-        <v>5.6000000000000004E-13</v>
-      </c>
-      <c r="C330" t="s">
-        <v>18</v>
-      </c>
-      <c r="E330" t="s">
-        <v>11</v>
-      </c>
-      <c r="F330" t="s">
-        <v>19</v>
-      </c>
-      <c r="G330" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="B330" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>144</v>
-      </c>
-      <c r="B331" s="1">
-        <v>8.3999999999999995E-13</v>
-      </c>
-      <c r="C331" t="s">
-        <v>18</v>
-      </c>
-      <c r="E331" t="s">
-        <v>11</v>
-      </c>
-      <c r="F331" t="s">
-        <v>19</v>
-      </c>
-      <c r="G331" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="B331" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>145</v>
-      </c>
-      <c r="B332" s="1">
-        <v>8.3999999999999995E-13</v>
-      </c>
-      <c r="C332" t="s">
-        <v>18</v>
-      </c>
-      <c r="E332" t="s">
-        <v>11</v>
-      </c>
-      <c r="F332" t="s">
-        <v>19</v>
-      </c>
-      <c r="G332" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A333" t="s">
-        <v>146</v>
-      </c>
-      <c r="B333" s="1">
-        <v>2.4999999999999999E-13</v>
-      </c>
-      <c r="C333" t="s">
-        <v>18</v>
-      </c>
-      <c r="E333" t="s">
-        <v>11</v>
-      </c>
-      <c r="F333" t="s">
-        <v>19</v>
-      </c>
-      <c r="G333" t="s">
-        <v>20</v>
-      </c>
+      <c r="A333" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F333" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H333" s="2"/>
+      <c r="I333" s="2"/>
+      <c r="J333" s="2"/>
+      <c r="K333" s="2"/>
+      <c r="L333" s="2"/>
+      <c r="M333" s="2"/>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="B334">
-        <v>3.93E-5</v>
+        <v>1</v>
       </c>
       <c r="C334" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D334" t="s">
+        <v>6</v>
       </c>
       <c r="E334" t="s">
         <v>11</v>
       </c>
       <c r="F334" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G334" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>147</v>
-      </c>
-      <c r="B335" s="1">
-        <v>7.5999999999999999E-13</v>
+        <v>127</v>
+      </c>
+      <c r="B335">
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="C335" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D335" t="s">
+        <v>6</v>
       </c>
       <c r="E335" t="s">
         <v>11</v>
       </c>
       <c r="F335" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G335" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>148</v>
-      </c>
-      <c r="B336" s="1">
-        <v>7.6000000000000004E-14</v>
+        <v>129</v>
+      </c>
+      <c r="B336">
+        <v>1.4400000000000001E-3</v>
       </c>
       <c r="C336" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D336" t="s">
+        <v>6</v>
       </c>
       <c r="E336" t="s">
         <v>11</v>
       </c>
       <c r="F336" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G336" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>149</v>
-      </c>
-      <c r="B337" s="1">
-        <v>8.3999999999999995E-13</v>
+        <v>131</v>
+      </c>
+      <c r="B337">
+        <v>0.11700000000000001</v>
       </c>
       <c r="C337" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D337" t="s">
+        <v>6</v>
       </c>
       <c r="E337" t="s">
         <v>11</v>
       </c>
       <c r="F337" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G337" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>150</v>
-      </c>
-      <c r="B338" s="1">
-        <v>1.5000000000000001E-12</v>
+        <v>100</v>
+      </c>
+      <c r="B338">
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="C338" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D338" t="s">
+        <v>38</v>
       </c>
       <c r="E338" t="s">
         <v>11</v>
       </c>
       <c r="F338" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G338" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>151</v>
-      </c>
-      <c r="B339" s="1">
-        <v>1E-10</v>
+        <v>133</v>
+      </c>
+      <c r="B339">
+        <v>4.2999999999999999E-4</v>
       </c>
       <c r="C339" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D339" t="s">
+        <v>6</v>
       </c>
       <c r="E339" t="s">
         <v>11</v>
       </c>
       <c r="F339" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G339" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B340">
-        <v>9.9999999999999995E-7</v>
+        <v>0.313</v>
       </c>
       <c r="C340" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D340" t="s">
+        <v>6</v>
       </c>
       <c r="E340" t="s">
         <v>11</v>
       </c>
       <c r="F340" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G340" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B341">
-        <v>2.5799999999999999E-6</v>
+        <v>1.4400000000000001E-3</v>
       </c>
       <c r="C341" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D341" t="s">
+        <v>6</v>
       </c>
       <c r="E341" t="s">
         <v>11</v>
       </c>
       <c r="F341" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G341" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>153</v>
-      </c>
-      <c r="B342" s="1">
-        <v>5.1000000000000005E-13</v>
+        <v>137</v>
+      </c>
+      <c r="B342">
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="C342" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D342" t="s">
+        <v>6</v>
       </c>
       <c r="E342" t="s">
         <v>11</v>
       </c>
       <c r="F342" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G342" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="B343">
-        <v>6.3E-5</v>
+        <v>0.248</v>
       </c>
       <c r="C343" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D343" t="s">
+        <v>6</v>
       </c>
       <c r="E343" t="s">
         <v>11</v>
       </c>
       <c r="F343" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G343" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B344">
-        <v>8.8999999999999995E-7</v>
+        <v>0.253</v>
       </c>
       <c r="C344" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D344" t="s">
+        <v>6</v>
       </c>
       <c r="E344" t="s">
         <v>11</v>
       </c>
       <c r="F344" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G344" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="B345">
-        <v>8.8999999999999995E-7</v>
+        <v>1.45</v>
       </c>
       <c r="C345" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D345" t="s">
+        <v>6</v>
       </c>
       <c r="E345" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F345" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G345" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A346" t="s">
-        <v>156</v>
-      </c>
-      <c r="B346" s="1">
-        <v>1.1200000000000001E-11</v>
-      </c>
-      <c r="C346" t="s">
-        <v>18</v>
-      </c>
-      <c r="E346" t="s">
-        <v>11</v>
-      </c>
-      <c r="F346" t="s">
-        <v>19</v>
-      </c>
-      <c r="G346" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A347" t="s">
-        <v>157</v>
-      </c>
-      <c r="B347">
-        <v>2.8099999999999999E-7</v>
-      </c>
-      <c r="C347" t="s">
-        <v>18</v>
-      </c>
-      <c r="E347" t="s">
-        <v>11</v>
-      </c>
-      <c r="F347" t="s">
-        <v>19</v>
-      </c>
-      <c r="G347" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A347" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>158</v>
-      </c>
-      <c r="B348" s="1">
-        <v>1.5000000000000001E-12</v>
-      </c>
-      <c r="C348" t="s">
-        <v>18</v>
-      </c>
-      <c r="E348" t="s">
-        <v>11</v>
-      </c>
-      <c r="F348" t="s">
-        <v>19</v>
-      </c>
-      <c r="G348" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="B348" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
+        <v>5</v>
+      </c>
+      <c r="B349" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>7</v>
+      </c>
+      <c r="B350" t="s">
         <v>160</v>
       </c>
-      <c r="B349">
-        <v>1</v>
-      </c>
-      <c r="C349" t="s">
-        <v>22</v>
-      </c>
-      <c r="D349" t="s">
-        <v>6</v>
-      </c>
-      <c r="E349" t="s">
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>8</v>
+      </c>
+      <c r="B351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>10</v>
+      </c>
+      <c r="B352" t="s">
         <v>61</v>
-      </c>
-      <c r="G349" t="s">
-        <v>23</v>
-      </c>
-      <c r="H349" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A352" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>3</v>
-      </c>
-      <c r="B353" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A354" t="s">
+      <c r="A354" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D354" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B354" t="s">
-        <v>6</v>
-      </c>
+      <c r="E354" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F354" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H354" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I354" s="2"/>
+      <c r="J354" s="2"/>
+      <c r="K354" s="2"/>
+      <c r="L354" s="2"/>
+      <c r="M354" s="2"/>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>7</v>
-      </c>
-      <c r="B355" t="s">
-        <v>171</v>
+        <v>142</v>
+      </c>
+      <c r="B355" s="1">
+        <v>1.2E-10</v>
+      </c>
+      <c r="C355" t="s">
+        <v>18</v>
+      </c>
+      <c r="E355" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" t="s">
+        <v>19</v>
+      </c>
+      <c r="G355" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>8</v>
-      </c>
-      <c r="B356" t="s">
-        <v>9</v>
+        <v>143</v>
+      </c>
+      <c r="B356" s="1">
+        <v>5.6000000000000004E-13</v>
+      </c>
+      <c r="C356" t="s">
+        <v>18</v>
+      </c>
+      <c r="E356" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" t="s">
+        <v>19</v>
+      </c>
+      <c r="G356" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>10</v>
-      </c>
-      <c r="B357" t="s">
-        <v>11</v>
+        <v>144</v>
+      </c>
+      <c r="B357" s="1">
+        <v>8.3999999999999995E-13</v>
+      </c>
+      <c r="C357" t="s">
+        <v>18</v>
+      </c>
+      <c r="E357" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" t="s">
+        <v>19</v>
+      </c>
+      <c r="G357" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>12</v>
+        <v>145</v>
+      </c>
+      <c r="B358" s="1">
+        <v>8.3999999999999995E-13</v>
+      </c>
+      <c r="C358" t="s">
+        <v>18</v>
+      </c>
+      <c r="E358" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" t="s">
+        <v>19</v>
+      </c>
+      <c r="G358" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A359" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D359" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G359" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H359" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I359" s="2"/>
-      <c r="J359" s="2"/>
-      <c r="K359" s="2"/>
-      <c r="L359" s="2"/>
-      <c r="M359" s="2"/>
+      <c r="A359" t="s">
+        <v>146</v>
+      </c>
+      <c r="B359" s="1">
+        <v>2.4999999999999999E-13</v>
+      </c>
+      <c r="C359" t="s">
+        <v>18</v>
+      </c>
+      <c r="E359" t="s">
+        <v>11</v>
+      </c>
+      <c r="F359" t="s">
+        <v>19</v>
+      </c>
+      <c r="G359" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B360">
-        <v>3.86E-4</v>
+        <v>3.93E-5</v>
       </c>
       <c r="C360" t="s">
         <v>18</v>
@@ -7705,163 +7760,250 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>171</v>
-      </c>
-      <c r="B361">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="B361" s="1">
+        <v>7.5999999999999999E-13</v>
       </c>
       <c r="C361" t="s">
-        <v>22</v>
-      </c>
-      <c r="D361" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E361" t="s">
         <v>11</v>
       </c>
+      <c r="F361" t="s">
+        <v>19</v>
+      </c>
       <c r="G361" t="s">
-        <v>23</v>
-      </c>
-      <c r="H361" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>159</v>
-      </c>
-      <c r="B362">
-        <v>1</v>
+        <v>148</v>
+      </c>
+      <c r="B362" s="1">
+        <v>7.6000000000000004E-14</v>
       </c>
       <c r="C362" t="s">
-        <v>22</v>
-      </c>
-      <c r="D362" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E362" t="s">
         <v>11</v>
       </c>
+      <c r="F362" t="s">
+        <v>19</v>
+      </c>
       <c r="G362" t="s">
-        <v>26</v>
-      </c>
-      <c r="H362" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>57</v>
-      </c>
-      <c r="B363">
-        <v>1.3099999999999999E-2</v>
+        <v>149</v>
+      </c>
+      <c r="B363" s="1">
+        <v>8.3999999999999995E-13</v>
       </c>
       <c r="C363" t="s">
-        <v>25</v>
-      </c>
-      <c r="D363" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E363" t="s">
-        <v>58</v>
+        <v>11</v>
+      </c>
+      <c r="F363" t="s">
+        <v>19</v>
       </c>
       <c r="G363" t="s">
-        <v>26</v>
-      </c>
-      <c r="H363" t="s">
-        <v>59</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>150</v>
+      </c>
+      <c r="B364" s="1">
+        <v>1.5000000000000001E-12</v>
+      </c>
+      <c r="C364" t="s">
+        <v>18</v>
+      </c>
+      <c r="E364" t="s">
+        <v>11</v>
+      </c>
+      <c r="F364" t="s">
+        <v>19</v>
+      </c>
+      <c r="G364" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A365" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>172</v>
+      <c r="A365" t="s">
+        <v>151</v>
+      </c>
+      <c r="B365" s="1">
+        <v>1E-10</v>
+      </c>
+      <c r="C365" t="s">
+        <v>18</v>
+      </c>
+      <c r="E365" t="s">
+        <v>11</v>
+      </c>
+      <c r="F365" t="s">
+        <v>19</v>
+      </c>
+      <c r="G365" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>3</v>
-      </c>
-      <c r="B366" t="s">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="B366">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C366" t="s">
+        <v>18</v>
+      </c>
+      <c r="E366" t="s">
+        <v>11</v>
+      </c>
+      <c r="F366" t="s">
+        <v>19</v>
+      </c>
+      <c r="G366" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>5</v>
-      </c>
-      <c r="B367" t="s">
-        <v>6</v>
+        <v>152</v>
+      </c>
+      <c r="B367">
+        <v>2.5799999999999999E-6</v>
+      </c>
+      <c r="C367" t="s">
+        <v>18</v>
+      </c>
+      <c r="E367" t="s">
+        <v>11</v>
+      </c>
+      <c r="F367" t="s">
+        <v>19</v>
+      </c>
+      <c r="G367" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>7</v>
-      </c>
-      <c r="B368" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+      <c r="B368" s="1">
+        <v>5.1000000000000005E-13</v>
+      </c>
+      <c r="C368" t="s">
+        <v>18</v>
+      </c>
+      <c r="E368" t="s">
+        <v>11</v>
+      </c>
+      <c r="F368" t="s">
+        <v>19</v>
+      </c>
+      <c r="G368" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>8</v>
-      </c>
-      <c r="B369" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="B369">
+        <v>6.3E-5</v>
+      </c>
+      <c r="C369" t="s">
+        <v>18</v>
+      </c>
+      <c r="E369" t="s">
+        <v>11</v>
+      </c>
+      <c r="F369" t="s">
+        <v>19</v>
+      </c>
+      <c r="G369" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>10</v>
-      </c>
-      <c r="B370" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="B370">
+        <v>8.8999999999999995E-7</v>
+      </c>
+      <c r="C370" t="s">
+        <v>18</v>
+      </c>
+      <c r="E370" t="s">
+        <v>11</v>
+      </c>
+      <c r="F370" t="s">
+        <v>19</v>
+      </c>
+      <c r="G370" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A372" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D372" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E372" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F372" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G372" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H372" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I372" s="2"/>
-      <c r="J372" s="2"/>
-      <c r="K372" s="2"/>
-      <c r="L372" s="2"/>
-      <c r="M372" s="2"/>
-    </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="B371">
+        <v>8.8999999999999995E-7</v>
+      </c>
+      <c r="C371" t="s">
+        <v>18</v>
+      </c>
+      <c r="E371" t="s">
+        <v>11</v>
+      </c>
+      <c r="F371" t="s">
+        <v>19</v>
+      </c>
+      <c r="G371" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>156</v>
+      </c>
+      <c r="B372" s="1">
+        <v>1.1200000000000001E-11</v>
+      </c>
+      <c r="C372" t="s">
+        <v>18</v>
+      </c>
+      <c r="E372" t="s">
+        <v>11</v>
+      </c>
+      <c r="F372" t="s">
+        <v>19</v>
+      </c>
+      <c r="G372" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="B373">
-        <v>4.4700000000000002E-4</v>
+        <v>2.8099999999999999E-7</v>
       </c>
       <c r="C373" t="s">
         <v>18</v>
@@ -7876,32 +8018,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>172</v>
-      </c>
-      <c r="B374">
-        <v>1</v>
+        <v>158</v>
+      </c>
+      <c r="B374" s="1">
+        <v>1.5000000000000001E-12</v>
       </c>
       <c r="C374" t="s">
-        <v>22</v>
-      </c>
-      <c r="D374" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E374" t="s">
         <v>11</v>
       </c>
+      <c r="F374" t="s">
+        <v>19</v>
+      </c>
       <c r="G374" t="s">
-        <v>23</v>
-      </c>
-      <c r="H374" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -7913,40 +8052,363 @@
         <v>6</v>
       </c>
       <c r="E375" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G375" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H375" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A378" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>3</v>
+      </c>
+      <c r="B379" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>5</v>
+      </c>
+      <c r="B380" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>7</v>
+      </c>
+      <c r="B381" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>8</v>
+      </c>
+      <c r="B382" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>10</v>
+      </c>
+      <c r="B383" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A385" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F385" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G385" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I385" s="2"/>
+      <c r="J385" s="2"/>
+      <c r="K385" s="2"/>
+      <c r="L385" s="2"/>
+      <c r="M385" s="2"/>
+    </row>
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>43</v>
+      </c>
+      <c r="B386">
+        <v>3.86E-4</v>
+      </c>
+      <c r="C386" t="s">
+        <v>18</v>
+      </c>
+      <c r="E386" t="s">
+        <v>11</v>
+      </c>
+      <c r="F386" t="s">
+        <v>19</v>
+      </c>
+      <c r="G386" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>171</v>
+      </c>
+      <c r="B387">
+        <v>1</v>
+      </c>
+      <c r="C387" t="s">
+        <v>22</v>
+      </c>
+      <c r="D387" t="s">
+        <v>6</v>
+      </c>
+      <c r="E387" t="s">
+        <v>11</v>
+      </c>
+      <c r="G387" t="s">
+        <v>23</v>
+      </c>
+      <c r="H387" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A376" t="s">
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388" t="s">
+        <v>22</v>
+      </c>
+      <c r="D388" t="s">
+        <v>6</v>
+      </c>
+      <c r="E388" t="s">
+        <v>11</v>
+      </c>
+      <c r="G388" t="s">
+        <v>26</v>
+      </c>
+      <c r="H388" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
         <v>57</v>
       </c>
-      <c r="B376">
+      <c r="B389">
         <v>1.3099999999999999E-2</v>
       </c>
-      <c r="C376" t="s">
-        <v>25</v>
-      </c>
-      <c r="D376" t="s">
-        <v>6</v>
-      </c>
-      <c r="E376" t="s">
+      <c r="C389" t="s">
+        <v>25</v>
+      </c>
+      <c r="D389" t="s">
+        <v>6</v>
+      </c>
+      <c r="E389" t="s">
         <v>58</v>
       </c>
-      <c r="G376" t="s">
-        <v>26</v>
-      </c>
-      <c r="H376" t="s">
+      <c r="G389" t="s">
+        <v>26</v>
+      </c>
+      <c r="H389" t="s">
         <v>59</v>
       </c>
     </row>
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A391" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>3</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>5</v>
+      </c>
+      <c r="B393" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>7</v>
+      </c>
+      <c r="B394" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>8</v>
+      </c>
+      <c r="B395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>10</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A398" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F398" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G398" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I398" s="2"/>
+      <c r="J398" s="2"/>
+      <c r="K398" s="2"/>
+      <c r="L398" s="2"/>
+      <c r="M398" s="2"/>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>43</v>
+      </c>
+      <c r="B399">
+        <v>4.4700000000000002E-4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>18</v>
+      </c>
+      <c r="E399" t="s">
+        <v>11</v>
+      </c>
+      <c r="F399" t="s">
+        <v>19</v>
+      </c>
+      <c r="G399" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>172</v>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400" t="s">
+        <v>22</v>
+      </c>
+      <c r="D400" t="s">
+        <v>6</v>
+      </c>
+      <c r="E400" t="s">
+        <v>11</v>
+      </c>
+      <c r="G400" t="s">
+        <v>23</v>
+      </c>
+      <c r="H400" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>159</v>
+      </c>
+      <c r="B401">
+        <v>1</v>
+      </c>
+      <c r="C401" t="s">
+        <v>22</v>
+      </c>
+      <c r="D401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E401" t="s">
+        <v>11</v>
+      </c>
+      <c r="G401" t="s">
+        <v>26</v>
+      </c>
+      <c r="H401" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>57</v>
+      </c>
+      <c r="B402">
+        <v>1.3099999999999999E-2</v>
+      </c>
+      <c r="C402" t="s">
+        <v>25</v>
+      </c>
+      <c r="D402" t="s">
+        <v>6</v>
+      </c>
+      <c r="E402" t="s">
+        <v>58</v>
+      </c>
+      <c r="G402" t="s">
+        <v>26</v>
+      </c>
+      <c r="H402" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M377" xr:uid="{7263A38E-0BDC-2843-B92F-206445D00D40}"/>
+  <autoFilter ref="A1:M403" xr:uid="{7263A38E-0BDC-2843-B92F-206445D00D40}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
